--- a/src/main/resources/data/cust_mgr_hierarchy.xlsx
+++ b/src/main/resources/data/cust_mgr_hierarchy.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9324"/>
+    <workbookView windowWidth="23040" windowHeight="9324" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="004012022" sheetId="1" r:id="rId1"/>
+    <sheet name="004012020" sheetId="2" r:id="rId2"/>
+    <sheet name="004011006" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="58">
   <si>
     <t>custMgrBigRegionCode</t>
   </si>
@@ -118,7 +118,7 @@
     <t>004012020</t>
   </si>
   <si>
-    <t>广深大区</t>
+    <t>广东大区</t>
   </si>
   <si>
     <t>004012020012</t>
@@ -158,6 +158,18 @@
   </si>
   <si>
     <t>黄佳云</t>
+  </si>
+  <si>
+    <t>684BF6BD5829D2613460D115B0C8B4AD</t>
+  </si>
+  <si>
+    <t>陈其祥</t>
+  </si>
+  <si>
+    <t>8c9d06c140244485b64a837510f244e2</t>
+  </si>
+  <si>
+    <t>陈康生</t>
   </si>
   <si>
     <t>004011006</t>
@@ -806,7 +818,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -814,6 +826,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1129,7 +1142,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="23.3333333333333" customWidth="1"/>
@@ -1169,13 +1182,13 @@
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
@@ -1195,13 +1208,13 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
@@ -1221,13 +1234,13 @@
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:8">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
@@ -1247,13 +1260,13 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
@@ -1267,13 +1280,13 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
@@ -1293,13 +1306,13 @@
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:8">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
@@ -1319,13 +1332,13 @@
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:8">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
@@ -1345,151 +1358,8 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1501,9 +1371,168 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="23.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="12.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="21.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="15.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="36.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="16.8888888888889" customWidth="1"/>
+    <col min="7" max="7" width="35.5555555555556" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1513,9 +1542,104 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="14.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="12.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="21.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="17.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="37.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="17.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/src/main/resources/data/cust_mgr_hierarchy.xlsx
+++ b/src/main/resources/data/cust_mgr_hierarchy.xlsx
@@ -10,6 +10,7 @@
     <sheet name="004012022" sheetId="1" r:id="rId1"/>
     <sheet name="004012020" sheetId="2" r:id="rId2"/>
     <sheet name="004011006" sheetId="3" r:id="rId3"/>
+    <sheet name="004011009" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="68">
   <si>
     <t>custMgrBigRegionCode</t>
   </si>
@@ -203,6 +204,36 @@
   </si>
   <si>
     <t>杜虎彪</t>
+  </si>
+  <si>
+    <t>004011009</t>
+  </si>
+  <si>
+    <t>浙江大区</t>
+  </si>
+  <si>
+    <t>004011009001003</t>
+  </si>
+  <si>
+    <t>销售一组</t>
+  </si>
+  <si>
+    <t>c4f1cfad504e49589169124f9dbdb36d</t>
+  </si>
+  <si>
+    <t>裴华-浙江财代</t>
+  </si>
+  <si>
+    <t>004011009002</t>
+  </si>
+  <si>
+    <t>宁波销售团队</t>
+  </si>
+  <si>
+    <t>6015A9C5C639B82BE6C3EB2ACC783B5D</t>
+  </si>
+  <si>
+    <t>运维账号-宁波</t>
   </si>
 </sst>
 </file>
@@ -215,9 +246,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -688,145 +727,150 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1149,7 +1193,7 @@
     <col min="2" max="2" width="22.4444444444444" customWidth="1"/>
     <col min="3" max="3" width="18.8888888888889" customWidth="1"/>
     <col min="4" max="4" width="22.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="34.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.6666666666667" style="3" customWidth="1"/>
     <col min="6" max="6" width="15.2222222222222" customWidth="1"/>
     <col min="7" max="7" width="33.2222222222222" customWidth="1"/>
     <col min="8" max="8" width="12.4444444444444" customWidth="1"/>
@@ -1168,7 +1212,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1182,19 +1226,19 @@
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
@@ -1208,19 +1252,19 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F3" t="s">
@@ -1234,19 +1278,19 @@
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:8">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F4" t="s">
@@ -1260,106 +1304,106 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:8">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:8">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1375,9 +1419,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="23.3333333333333" customWidth="1"/>
-    <col min="2" max="2" width="12.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="22.8888888888889" customWidth="1"/>
     <col min="3" max="3" width="21.1111111111111" customWidth="1"/>
-    <col min="4" max="4" width="15.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="21.4444444444444" customWidth="1"/>
     <col min="5" max="5" width="36.4444444444444" customWidth="1"/>
     <col min="6" max="6" width="16.8888888888889" customWidth="1"/>
     <col min="7" max="7" width="35.5555555555556" customWidth="1"/>
@@ -1396,7 +1440,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1410,42 +1454,42 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D2" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G3" t="s">
@@ -1453,82 +1497,82 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D5" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1566,7 +1610,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1580,13 +1624,13 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D2" t="s">
@@ -1600,13 +1644,13 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D3" t="s">
@@ -1620,22 +1664,22 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D4" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1644,4 +1688,91 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="27.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="28.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="23.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="23.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="35.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="22.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="13.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>